--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486259_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486259_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8033</v>
+        <v>6.2865</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0012</v>
+        <v>3.8029</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8021</v>
+        <v>2.4836</v>
       </c>
       <c r="G2" t="n">
         <v>1.6559</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5824</v>
+        <v>1.0656</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7487</v>
+        <v>0.5504</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8337</v>
+        <v>0.5152</v>
       </c>
       <c r="V2" t="n">
         <v>2.2599</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4452</v>
+        <v>5.2721</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8084</v>
+        <v>2.7277</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6369</v>
+        <v>2.5444</v>
       </c>
       <c r="G3" t="n">
         <v>-0.1932</v>
@@ -688,13 +688,13 @@
         <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5568</v>
+        <v>0.2701</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7413999999999999</v>
+        <v>0.1779</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1847</v>
+        <v>0.0922</v>
       </c>
       <c r="V3" t="n">
         <v>3.0202</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. LOBO MARTORELL</t>
+          <t>S. LITTLESON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3761</v>
+        <v>5.0541</v>
       </c>
       <c r="E4" t="n">
-        <v>6.5599</v>
+        <v>4.0392</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.1838</v>
+        <v>1.0149</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5341</v>
+        <v>7.3285</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5506</v>
+        <v>-1.6545</v>
       </c>
       <c r="I4" t="n">
-        <v>5.0848</v>
+        <v>8.983000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>5.8499</v>
+        <v>7.1852</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8942</v>
+        <v>-0.5411</v>
       </c>
       <c r="L4" t="n">
-        <v>4.9557</v>
+        <v>7.7264</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3158</v>
+        <v>0.1433</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4449</v>
+        <v>-1.1134</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1291</v>
+        <v>1.2566</v>
       </c>
       <c r="P4" t="n">
         <v>-1.7401</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R4" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.113</v>
+        <v>-0.1439</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0601</v>
+        <v>0.1166</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.173</v>
+        <v>-0.2605</v>
       </c>
       <c r="V4" t="n">
-        <v>1.695</v>
+        <v>-0.3904</v>
       </c>
       <c r="W4" t="n">
-        <v>2.8249</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. LITTLESON</t>
+          <t>J. LOBO MARTORELL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.268</v>
+        <v>4.7096</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5922</v>
+        <v>6.5851</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6758</v>
+        <v>-1.8756</v>
       </c>
       <c r="G5" t="n">
-        <v>7.3285</v>
+        <v>4.5341</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6545</v>
+        <v>-0.5506</v>
       </c>
       <c r="I5" t="n">
-        <v>8.983000000000001</v>
+        <v>5.0848</v>
       </c>
       <c r="J5" t="n">
-        <v>7.1852</v>
+        <v>5.8499</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5411</v>
+        <v>0.8942</v>
       </c>
       <c r="L5" t="n">
-        <v>7.7264</v>
+        <v>4.9557</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1433</v>
+        <v>-1.3158</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1134</v>
+        <v>-1.4449</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2566</v>
+        <v>0.1291</v>
       </c>
       <c r="P5" t="n">
         <v>-1.7401</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.93</v>
+        <v>0.2205</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3305</v>
+        <v>0.0853</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5995</v>
+        <v>0.1352</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3904</v>
+        <v>1.695</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.8249</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3904</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3257</v>
+        <v>3.1756</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7472</v>
+        <v>1.443</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5785</v>
+        <v>1.7326</v>
       </c>
       <c r="G6" t="n">
         <v>5.403</v>
@@ -922,13 +922,13 @@
         <v>1.9576</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6423</v>
+        <v>0.2076</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6044</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0379</v>
+        <v>0.1163</v>
       </c>
       <c r="V6" t="n">
         <v>-1.13</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5028</v>
+        <v>1.3795</v>
       </c>
       <c r="E7" t="n">
         <v>2.4472</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9445</v>
+        <v>-1.0678</v>
       </c>
       <c r="G7" t="n">
         <v>0.9261</v>
@@ -1000,13 +1000,13 @@
         <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7518</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="T7" t="n">
         <v>0.3341</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4177</v>
+        <v>0.2944</v>
       </c>
       <c r="V7" t="n">
         <v>1.13</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8912</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="E8" t="n">
         <v>0.8172</v>
       </c>
       <c r="F8" t="n">
-        <v>0.074</v>
+        <v>0.0432</v>
       </c>
       <c r="G8" t="n">
         <v>0.6378</v>
@@ -1078,13 +1078,13 @@
         <v>0.2175</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0359</v>
+        <v>0.0051</v>
       </c>
       <c r="T8" t="n">
         <v>-0.137</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1729</v>
+        <v>0.1421</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8854</v>
+        <v>0.0916</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6904</v>
+        <v>0.0198</v>
       </c>
       <c r="F9" t="n">
-        <v>0.195</v>
+        <v>0.0717</v>
       </c>
       <c r="G9" t="n">
         <v>1.791</v>
@@ -1156,13 +1156,13 @@
         <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4848</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2161</v>
+        <v>0.5456</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2687</v>
+        <v>0.1454</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5204</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. SCHOTT</t>
+          <t>E. WEMBI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8625</v>
+        <v>-0.5851</v>
       </c>
       <c r="E10" t="n">
-        <v>1.83</v>
+        <v>0.7709</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6925</v>
+        <v>-1.3561</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9402</v>
+        <v>-0.4681</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.882</v>
+        <v>-2.1352</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0582</v>
+        <v>1.667</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4752</v>
+        <v>0.7632</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1309</v>
+        <v>-0.6903</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3442</v>
+        <v>1.4535</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4153</v>
+        <v>-1.2313</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0129</v>
+        <v>-1.4449</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4024</v>
+        <v>0.2136</v>
       </c>
       <c r="P10" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5329</v>
+        <v>0.1652</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1596</v>
+        <v>-0.1875</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3732</v>
+        <v>0.3527</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8902</v>
+        <v>-0.9347</v>
       </c>
       <c r="W10" t="n">
         <v>0.1952</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.0854</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. WEMBI</t>
+          <t>F. SCHOTT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.884</v>
+        <v>-1.5445</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4104</v>
+        <v>1.2712</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2944</v>
+        <v>-2.8158</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4681</v>
+        <v>-0.9402</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1352</v>
+        <v>-0.882</v>
       </c>
       <c r="I11" t="n">
-        <v>1.667</v>
+        <v>-0.0582</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7632</v>
+        <v>0.4752</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6903</v>
+        <v>0.1309</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4535</v>
+        <v>0.3442</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2313</v>
+        <v>-1.4153</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4449</v>
+        <v>-1.0129</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2136</v>
+        <v>-0.4024</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1336</v>
+        <v>0.8508</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.548</v>
+        <v>0.6009</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4143</v>
+        <v>0.2499</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9347</v>
+        <v>-1.8902</v>
       </c>
       <c r="W11" t="n">
         <v>0.1952</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.13</v>
+        <v>-2.0854</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.957</v>
+        <v>-2.1689</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.3981</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8942</v>
+        <v>-1.7709</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2122</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4728</v>
+        <v>0.2608</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4711</v>
+        <v>0.1358</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0017</v>
+        <v>0.125</v>
       </c>
       <c r="V12" t="n">
         <v>-1.13</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>21.7942</v>
+        <v>22.5309</v>
       </c>
       <c r="E13" t="n">
-        <v>22.8413</v>
+        <v>23.5261</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0471</v>
+        <v>-0.9957999999999989</v>
       </c>
       <c r="G13" t="n">
         <v>20.4627</v>
@@ -1468,13 +1468,13 @@
         <v>11.9628</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4849</v>
+        <v>4.2213</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6284</v>
+        <v>2.3134</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8565</v>
+        <v>1.9079</v>
       </c>
       <c r="V13" t="n">
         <v>1.109399999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3354</v>
+        <v>3.6514</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3992</v>
+        <v>3.6227</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.06370000000000001</v>
+        <v>0.0287</v>
       </c>
       <c r="G14" t="n">
         <v>1.4108</v>
@@ -1546,13 +1546,13 @@
         <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2929</v>
+        <v>0.0231</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.125</v>
+        <v>0.0985</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1679</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>1.13</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5728</v>
+        <v>1.2595</v>
       </c>
       <c r="E15" t="n">
         <v>2.0042</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4313</v>
+        <v>-0.7447</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5831</v>
@@ -1624,13 +1624,13 @@
         <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3082</v>
+        <v>-0.0051</v>
       </c>
       <c r="T15" t="n">
         <v>-0.4194</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7276</v>
+        <v>0.4143</v>
       </c>
       <c r="V15" t="n">
         <v>0.7602</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2064</v>
+        <v>0.8468</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3344</v>
+        <v>1.8873</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1279</v>
+        <v>-1.0405</v>
       </c>
       <c r="G16" t="n">
         <v>-1.4492</v>
@@ -1702,13 +1702,13 @@
         <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>0.853</v>
+        <v>0.4933</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8051</v>
+        <v>0.3581</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0478</v>
+        <v>0.1352</v>
       </c>
       <c r="V16" t="n">
         <v>2.4552</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.26</v>
+        <v>-0.025</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1834</v>
+        <v>-0.0716</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0767</v>
+        <v>0.0466</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0682</v>
@@ -1780,13 +1780,13 @@
         <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0618</v>
+        <v>-0.8268</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.536</v>
+        <v>-0.4242</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5259</v>
+        <v>-0.4026</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5228</v>
+        <v>-1.4432</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7594</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2822</v>
+        <v>-1.979</v>
       </c>
       <c r="G18" t="n">
         <v>-2.9265</v>
@@ -1858,13 +1858,13 @@
         <v>2.3926</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2313</v>
+        <v>0.3109</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4627</v>
+        <v>0.2392</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2313</v>
+        <v>0.0718</v>
       </c>
       <c r="V18" t="n">
         <v>2.2599</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9078</v>
+        <v>-1.8885</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.649</v>
+        <v>-0.5372</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2588</v>
+        <v>-1.3513</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0326</v>
@@ -1936,13 +1936,13 @@
         <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4402</v>
+        <v>-0.4209</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.274</v>
+        <v>-0.1622</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1662</v>
+        <v>-0.2587</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1084</v>
+        <v>-2.1277</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9933</v>
+        <v>-1.105</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1151</v>
+        <v>-1.0227</v>
       </c>
       <c r="G20" t="n">
         <v>-3.7971</v>
@@ -2014,13 +2014,13 @@
         <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0513</v>
+        <v>-0.0706</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0721</v>
+        <v>-0.0396</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1234</v>
+        <v>-0.031</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5883</v>
+        <v>-2.9968</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6273</v>
+        <v>-0.8508</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9611</v>
+        <v>-2.146</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2938</v>
@@ -2092,13 +2092,13 @@
         <v>1.7401</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0548</v>
+        <v>-0.4633</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2019</v>
+        <v>-0.4254</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1471</v>
+        <v>-0.0379</v>
       </c>
       <c r="V21" t="n">
         <v>0.1952</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6116</v>
+        <v>-3.6668</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1364</v>
+        <v>-1.2482</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4752</v>
+        <v>-2.4186</v>
       </c>
       <c r="G22" t="n">
         <v>-3.8289</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3476</v>
+        <v>-0.4029</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1454</v>
+        <v>-0.2572</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2023</v>
+        <v>-0.1457</v>
       </c>
       <c r="V22" t="n">
         <v>0.5649999999999999</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7082</v>
+        <v>-4.5541</v>
       </c>
       <c r="E23" t="n">
         <v>-2.1731</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5351</v>
+        <v>-2.381</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4685</v>
@@ -2248,13 +2248,13 @@
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1098</v>
+        <v>-0.9556</v>
       </c>
       <c r="T23" t="n">
         <v>-0.536</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5738</v>
+        <v>-0.4197</v>
       </c>
       <c r="V23" t="n">
         <v>-1.695</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-11.2018</v>
+        <v>-10.1048</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6876</v>
+        <v>-1.0171</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.514099999999999</v>
+        <v>-9.0877</v>
       </c>
       <c r="G24" t="n">
         <v>-4.4254</v>
@@ -2326,13 +2326,13 @@
         <v>1.7401</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5191</v>
+        <v>-0.4221</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9589</v>
+        <v>-0.2884</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5601</v>
+        <v>-0.1337</v>
       </c>
       <c r="V24" t="n">
         <v>-6.7798</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-21.7943</v>
+        <v>-21.0492</v>
       </c>
       <c r="E25" t="n">
-        <v>1.047099999999999</v>
+        <v>1.047000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-22.8412</v>
+        <v>-22.0962</v>
       </c>
       <c r="G25" t="n">
         <v>-20.4625</v>
@@ -2404,13 +2404,13 @@
         <v>15.2255</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.485</v>
+        <v>-2.74</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.8567</v>
+        <v>-1.8566</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.6284</v>
+        <v>-0.8834000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-1.109300000000001</v>
